--- a/02-Execucao/05-Comentarios_Gestor/02-Avaliacao_Comentarios_Gestor/individuais/secao-2/avaliacoes_modelos.xlsx
+++ b/02-Execucao/05-Comentarios_Gestor/02-Avaliacao_Comentarios_Gestor/individuais/secao-2/avaliacoes_modelos.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escopo seção 2" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Avaliações'!$A$1:$X$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Avaliações'!$A$1:$X$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Motivos'!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Erros e ausências'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Escopo seção 2'!$A$1:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Erros e ausências'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Escopo seção 2'!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:X43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,8 +561,4084 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>26d5cb074edeb6a9c3c1b2f9558acfca35e06548c6954ffede7fbecf13ed61fa</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>q1001</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>nao_conforme</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>d) a organização designa responsáveis de cada área de negócio para a gestão dos respectivos sistemas informatizados</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Embora a instituição tenha apresentado novas normativas, incluindo a Política de Governança e Gestão de Tecnologia da Informação (publicada no DO em 11/05/2026) e resoluções sobre o Comitê Estratégico e o Comitê Gestor de Sistemas de Informação, os documentos não comprovam a designação formal de responsáveis dentro de cada área de negócio para a gestão dos seus sistemas informatizados específicos. A documentação apresentada foca em instâncias superiores de governança, mantendo a lacuna identificada na avaliação anterior sobre a descentralização da responsabilidade pelos sistemas nas áreas finalísticas.</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Ausência de designação formal de responsáveis de cada área de negócio para a gestão dos respectivos sistemas informatizados.</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>RESOLUÇÃO GPGJ nº 2.540 - CETI.pdf
+DO 11.05.2026.pdf
+RESOLUÇÃO CONJUNTA GPGJ-CGMP n° 24 - CGSI.pdf</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Política de Governança e Gestão de Tecnologia da Informação instituída pela Resolução GPGJ nº 2.785 (DO 11.05.2026)
+Resolução GPGJ nº 2.540 que define o CETI
+Resolução Conjunta GPGJ/CGMP nº 24 que define o CGSI</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Documento de Política de Governança e Gestão de TI (DO 11.05.2026)
+Resoluções GPGJ nº 2.540 e Conjunta GPGJ/CGMP nº 24</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:46:39.625853+00:00</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:47:11.592338+00:00</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>26d5cb074edeb6a9c3c1b2f9558acfca35e06548c6954ffede7fbecf13ed61fa</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>q1001</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>nao_conforme</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>q1001ext[D]</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Apesar do envio de novos normativos, como a Resolucao GPGJ n 2.785/2026 (Politica de Governanca e Gestao de TI) e resolucoes que instituem comites de TI (CETI, CGSI, CDTI), nao foi identificada nas evidencias apresentadas a designacao formal de responsaveis de cada area de negocio para a gestao de seus respectivos sistemas informatizados. Observa-se a instituicao de comites com representacao institucional e previsao de interlocucao com as areas de negocio (como para estabelecimento de acordos de nivel de servico), mas sem comprovar a designacao descentralizada de gestores ou donos de sistemas nas areas finalisticas.</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Ausencia de ato formal ou normativo que comprove a designacao de responsaveis especificos de cada area de negocio (fora da area de TI) para a gestao de seus respectivos sistemas informatizados.</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>DO 11.05.2026.pdf
+RESOLUCAO CONJUNTA GPGJ-CGMP n 24 - CGSI.pdf</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Resolucao GPGJ n 2.785/2026
+Comissao/Comite CGSI</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>DO 11.05.2026.pdf, paginas 4-5
+RESOLUCAO CONJUNTA GPGJ-CGMP n 24 - CGSI.pdf, pagina 1</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:05:14.947732+00:00</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:06:05.686676+00:00</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>26d5cb074edeb6a9c3c1b2f9558acfca35e06548c6954ffede7fbecf13ed61fa</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>q1001</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>nao_conforme</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>d) a organização designa responsáveis de cada área de negócio para a gestão dos respectivos sistemas informatizados</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>A avaliação anterior já havia identificado que a organização não designou formalmente responsáveis das áreas de negócio (áreas finalísticas) para a gestão dos sistemas informatizados. Os novos documentos apresentados (Resolução GPGJ nº 2.540/2023, Resolução GPGJ nº 2.785/2026, Resolução Conjunta GPGJ-CGMP nº 24/2020 e Resolução GPGJ nº 1.945/2014) tratam da criação e competências de comitês de TI (CETI, CDTI, CGSI) e da Política de Governança e Gestão de TI, definindo papéis e responsabilidades da área de TI e de instâncias de governança. No entanto, nenhum dos documentos demonstra a designação formal de responsáveis de cada área de negócio (áreas finalísticas) para a gestão dos respectivos sistemas informatizados, que é o requisito específico do item. A menção à 'gestão de comunicação com as áreas de negócio' (Art. 13, V, f da Res. 2.785/2026) e à interação com órgãos de execução (Art. 2º, II da Res. Conjunta 24/2020) não equivale à designação formal de responsáveis das áreas de negócio para a gestão dos sistemas.</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>],</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>],</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>],</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>],</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:22:39.221584+00:00</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:23:59.372251+00:00</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>37a7e82310fc8f4e1c95c8641435e4a08d47856abb0f1849e31cedcbd419ceda</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>q2102</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>b) o plano de TI é publicado na internet, para fácil acesso de partes interessadas e da sociedade</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>A organização apresentou evidências da publicação dos planos (PETI e PDTI) na internet, por meio do arquivo 'LINKS PETI e PDTI.txt', sanando a lacuna apontada na avaliação anterior que impedia a verificação da disponibilidade pública.</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>LINKS PETI e PDTI.txt</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo contendo os links de acesso aos planos publicados</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Documento referenciado no pacote de evidências</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:47:11.594566+00:00</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:48:13.466973+00:00</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>37a7e82310fc8f4e1c95c8641435e4a08d47856abb0f1849e31cedcbd419ceda</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>q2102</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>q2102ext[B]</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Nesta etapa de reavaliação, o MPERJ apresentou evidências robustas de que o plano de tecnologia da informação está publicado na internet para livre acesso da sociedade, sanando a lacuna apontada na auditoria anterior. O arquivo 'LINKS PETI e PDTI.txt' lista as URLs de publicação direta do Plano Estratégico de Tecnologia da Informação (PETI 2026/2027) e do Plano Diretor de Tecnologia da Informação (PDTI 2026). A vigência e a aprovação formal desses planos pela alta administração (CETI) foram demonstradas na ata de reunião realizada em 18/12/2025.</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>LINKS PETI e PDTI.txt
+Ata da Aprovação do PETI e do PDTI pelo CETI.pdf
+peti_2026_2027.pdf
+pdti_2026.pdf</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Links de acesso público no portal institucional do MPERJ
+Deliberação: o PETI 2026–2027 foi APROVADO por unanimidade.</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>LINKS PETI e PDTI.txt
+Ata da Aprovação do PETI e do PDTI pelo CETI.pdf, página 3</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:06:05.697178+00:00</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:07:15.791973+00:00</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>37a7e82310fc8f4e1c95c8641435e4a08d47856abb0f1849e31cedcbd419ceda</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>q2102</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>nao_conforme</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>q2102ext[B]</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>A evidência apresentada (PETI 2026/2027, Ata do CETI e Diário Oficial) comprova a existência e aprovação do plano de TI, mas não demonstra que o plano de TI foi publicado na internet para fácil acesso de partes interessadas e da sociedade. O arquivo 'LINKS PETI e PDTI.txt' está vazio e o Diário Oficial publicado contém apenas a Política de Governança e Gestão de TI (Resolução GPGJ nº 2.785/2026), não o PETI/PDTI em si. Não há link, registro de publicação em portal de transparência ou outra evidência verificável de publicação pública do plano.</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Não foram fornecidos links, registros de publicação em portal de transparência ou outras evidências que demonstrem a disponibilidade do plano de TI na internet para acesso de partes interessadas e da sociedade.</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>peti_2026_2027.pdf
+Ata da Aprovação do PETI e do PDTI pelo CETI.pdf
+DO 11.05.2026.pdf
+LINKS PETI e PDTI.txt</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>LINKS PETI e PDTI.txt (arquivo vazio)
+DO 11.05.2026.pdf - Resolução GPGJ nº 2.785/2026 institui a Política de Governança e Gestão de TI, não o PETI/PDTI</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>LINKS PETI e PDTI.txt
+DO 11.05.2026.pdf - Páginas 2 a 6</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:23:59.382566+00:00</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:25:24.895030+00:00</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>abf0c14116149ec884c3deb7e339f617e594bca8f72469070d714ae8628bd056</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>q2201</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2201. A organização elabora um catálogo de serviços de tecnologia da informação e monitora níveis de serviço.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>A organização apresentou evidências complementares que suprem as lacunas apontadas na avaliação anterior. O catálogo de serviços está detalhado no arquivo 'Catálogo de serviços.xlsx', e o monitoramento contínuo dos níveis de serviço é evidenciado pelos relatórios operacionais consolidados no 'BOOK METAS DE ATENDIMENTO - MPRJ - Maio 2026.pdf' e pelos dashboards do sistema Cherwell, que demonstram o acompanhamento de métricas de desempenho e SLA conforme pactuado.</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Catálogo de serviços.xlsx
+BOOK METAS DE ATENDIMENTO - MPRJ - Maio 2026.pdf
+Dashboard ANS - Backlog.png
+Dashboard ANS N1.png
+Dashboard ANS N2.png
+Dashboard ANS Projetos e Eventos.png</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Planilha contendo catálogo de serviços, categorias e tempos de contrato
+Relatórios operacionais de maio/2026 com indicadores de SLA e metas atingidas
+Dashboards do sistema Cherwell evidenciando o monitoramento de ANS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Arquivo Catálogo de serviços.xlsx
+Arquivo BOOK METAS DE ATENDIMENTO - MPRJ - Maio 2026.pdf</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:48:13.474545+00:00</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:50:08.102672+00:00</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>abf0c14116149ec884c3deb7e339f617e594bca8f72469070d714ae8628bd056</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>q2201</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2201. A organização elabora um catálogo de serviços de tecnologia da informação e monitora níveis de serviço.</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>A organização apresentou um robusto conjunto de novas evidências que comprovam de forma inequívoca tanto a elaboração de catálogo de serviços de TI quanto o monitoramento efetivo de níveis de serviço (SLA/ANS). Foram apresentados relatórios de performance detalhados, dashboards extraídos em tempo real do sistema de gestão Cherwell, além do book de metas de atendimento de maio de 2026 e do relatório de glosas do contrato de suporte técnico da prestadora IT2B, evidenciando a gestão ativa dos serviços de TI e a aplicação prática de sanções financeiras em caso de descumprimento das metas de SLA estabelecidas. As evidências saneiam integralmente as lacunas apontadas na etapa anterior.</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>BOOK METAS DE ATENDIMENTO - MPRJ - Maio 2026.pdf
+Catálogo de serviços.xlsx
+Relatórios Operacionais - Maio 2026.pdf
+Glosas_IT2B_2026.pdf
+Q2201 - Comentários.pdf</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Indicadores de SLA de atendimento telefônico, índice de chamadas abandonadas e primeiro atendimento (BOOK METAS DE ATENDIMENTO - MPRJ - Maio 2026.pdf, pgs. 2-8)
+Tabela de apuração de ANS contendo total de atendimentos, total geral de chamados, percentual de ANS alcançado e percentual de glosa correspondente ao mês de maio de 2026 (Glosas_IT2B_2026.pdf, pgs. 1-4)
+Estrutura completa do catálogo de serviços detalhada por equipe, serviço, categoria, prioridade e tempo de contrato em horas/minutos (Catálogo de serviços.xlsx, aba Catálogo de serviços)
+Esclarecimento sobre a parametrização do ANS no sistema Ivanti Cherwell Service Management (Q2201 - Comentários.pdf, pgs. 1-2)</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>BOOK METAS DE ATENDIMENTO - MPRJ - Maio 2026.pdf, páginas 2 a 8
+Glosas_IT2B_2026.pdf, páginas 1 a 4
+Q2201 - Comentários.pdf, páginas 1 a 3</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:07:15.799419+00:00</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:09:19.190328+00:00</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>96a850cf85ec953fe1948efc89d29f5d6039068d584194a642a6bfcc33d6ce84</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2203. A organização executa processo de gestão de configuração e ativos (de serviços de tecnologia da informação).</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>A organização apresentou evidências robustas de uma operação contínua de gestão de ativos através do sistema ASI. As novas planilhas de extração detalham inventários, detentores, localizações e status dos bens, sanando a lacuna de evidência operacional constatada na avaliação anterior.</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Extração Geral - ASI.xlsx
+Relatório de Detentores.xlsx
+Relatório de Status.xlsx</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Relatórios extraídos do sistema ASI contendo inventário detalhado de ativos de TI e mobiliário, incluindo números de série, localizações e status físico.</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Base de dados de inventário (ASI)</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:23:31.297331+00:00</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:24:41.811407+00:00</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>96a850cf85ec953fe1948efc89d29f5d6039068d584194a642a6bfcc33d6ce84</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>a) a organização mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>As planilhas enviadas comprovam a manutenção de uma base de dados estruturada e atualizada via sistema ASI, abrangendo ativos de TI e outros itens, o que permite o monitoramento consolidado de patrimônio e ativos.</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Extração Geral - ASI.xlsx
+Relatório de Detentores.xlsx
+Relatório de Status.xlsx</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Extratos detalhados de inventário demonstrando uma base consolidada de ativos com informações de localização, detentor e descrição técnica.</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Sistema ASI (Base de dados de inventário)</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:23:31.297331+00:00</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:24:41.811407+00:00</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>96a850cf85ec953fe1948efc89d29f5d6039068d584194a642a6bfcc33d6ce84</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>nao_conforme</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>b) a base de dados de configurações é utilizada como insumo para o planejamento e o acompanhamento das mudanças</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Embora o sistema ASI demonstre a capacidade técnica de controle de inventário, não foram apresentados registros, fluxos de trabalho ou evidências de que esta base seja efetivamente utilizada no processo de gestão de mudanças para planejamento e acompanhamento.</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Ausência de evidências da integração entre a base de inventário (ASI) e o fluxo de gestão de mudanças.</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>comentario_gestor.txt</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Nenhum registro operacional que conecte o inventário ao planejamento ou execução de mudanças em TI.</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:23:31.297331+00:00</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:24:41.811407+00:00</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>96a850cf85ec953fe1948efc89d29f5d6039068d584194a642a6bfcc33d6ce84</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>**2203. A organização executa processo de gestão de configuração e ativos (de serviços de tecnologia da informação).**</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>A organização comprovou a execução operacional do processo de gestão de ativos de tecnologia da informação ao apresentar relatórios detalhados extraídos de seu sistema corporativo de patrimônio (ASI), incluindo o controle físico de equipamentos de informática, especificações técnicas detalhadas de hardware (CPU, HD, RAM), identificação de detentores responsáveis e localizações específicas dos itens de TI (por exemplo, na Gerência de Manutenção de Informática). Essa documentação operacional robusta atende ao critério de demonstrar a execução prática do inventário e controle de ativos de TI, superando a lacuna apontada na etapa de avaliação anterior.</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Extração Geral - ASI.xlsx
+Relatório de Detentores.xlsx
+Relatório de Status.xlsx
+Q2203 Comentários.pdf</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>RelatorioAnaliticoBemMarcaModel contendo colunas como Patrimônio, Material, Marca, Modelo, Série e Conta Contábil de equipamentos de TIC
+RelatorioBensPorDetentor associando computadores Lenovo T14 e HP X360 aos respectivos detentores
+RelatorioAnaliticoBensMoveisPor descrevendo localização física detalhada de itens como aparelhos DVR e coletores de dados na Gerência de Manutenção de Informática
+A gestão de materiais de informática, bem como de outros itens da instituição, é realizada por meio do sistema ASI, uma plataforma que permite a realização de consultas por campos e filtros específicos, acompanhamentos dos registros de ciclo de vida dos bens...</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Aba RelatorioAnaliticoBemMarcaModel do arquivo Extração Geral - ASI.xlsx
+Aba RelatorioBensPorDetentor do arquivo Relatório de Detentores.xlsx
+Aba RelatorioAnaliticoBensMoveisPor do arquivo Relatório de Status.xlsx
+Páginas 1 a 12 do arquivo Q2203 Comentários.pdf</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:23:30.693339+00:00</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:24:43.199771+00:00</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>96a850cf85ec953fe1948efc89d29f5d6039068d584194a642a6bfcc33d6ce84</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>nao_conforme</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>q2203ext[A]</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Embora a organização tenha comprovado manter um controle minucioso e atualizado sobre as especificações técnicas e movimentações de seus ativos físicos de hardware de TI (computadores, notebooks, impressoras) por meio do sistema ASI, as evidências apresentadas mostram que o banco de dados tem foco eminentemente patrimonial e contábil. Não foram fornecidos mapas de configuração ou de relacionamento que vinculem esses ativos de infraestrutura de TI aos respectivos serviços de tecnologia da informação ofertados pela organização, de modo a registrar as interdependências entre serviços e ativos (como se requer de uma CMDB de TI).</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Ausência de registro das configurações de serviços de tecnologia da informação no banco de dados apresentado.
+Inexistência de mapeamento dos relacionamentos de dependência entre os ativos físicos/infraestrutura e os serviços de TI oferecidos pela organização.</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Extração Geral - ASI.xlsx
+Relatório de Detentores.xlsx
+Relatório de Status.xlsx
+Q2203 Comentários.pdf</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>A gestão de materiais de informática, bem como de outros itens da instituição, é realizada por meio do sistema ASI...
+Acompanhamentos dos registros de ciclo de vida dos bens, vinculação de processos e documentos correlatos e gama extensa de relatórios...</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Extração Geral - ASI.xlsx
+Relatório de Detentores.xlsx
+Relatório de Status.xlsx
+Páginas 1 a 12 do arquivo Q2203 Comentários.pdf</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:23:30.693339+00:00</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:24:43.199771+00:00</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>96a850cf85ec953fe1948efc89d29f5d6039068d584194a642a6bfcc33d6ce84</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>nao_conforme</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>q2203ext[B]</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>A documentação técnica do sistema ASI e os respectivos relatórios analíticos de patrimônio anexados focam na gestão logística, física e financeira dos bens. No entanto, não foi apresentada nenhuma evidência de natureza operacional (como tíquetes de mudança, ordens de serviço, relatórios de impacto ou fluxos formais de processos) que demonstre que esse banco de dados seja integrado ou utilizado de forma prática como insumo para apoiar a análise, o planejamento ou o acompanhamento das mudanças no ambiente tecnológico da instituição.</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Ausência de registros, fluxogramas, ordens de serviço ou registros do sistema de gestão de mudanças (como RFCs) demonstrando a consulta ou a integração prática da base de configurações de ativos como insumo para a tomada de decisão no planejamento ou acompanhamento de mudanças.</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Q2203 Comentários.pdf</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Descrição geral sobre as funcionalidades do sistema ASI quanto ao ciclo de vida patrimonial do bem, movimentação, atestos, responsáveis, detentores e cálculo de depreciação contábil.</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Páginas 1 a 12 do arquivo Q2203 Comentários.pdf</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:23:30.693339+00:00</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:24:43.199771+00:00</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>96a850cf85ec953fe1948efc89d29f5d6039068d584194a642a6bfcc33d6ce84</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2203. A organização executa processo de gestão de configuração e ativos (de serviços de tecnologia da informação).</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Adota em maior parte ou totalmente.</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>A evidência demonstra que a organização utiliza o sistema ASI (Sistema Integrado de Gestão) para a gestão de patrimônio e ativos de TI, com funcionalidades que permitem consulta, filtragem, acompanhamento do ciclo de vida dos bens, movimentações, inventários, levantamentos RFID, avaliações financeiras e emissão de relatórios variados. O manual online do sistema também está disponível. Os relatórios extraídos (Extração Geral - ASI.xlsx, Relatório de Detentores.xlsx, Relatório de Status.xlsx) confirmam a existência de um inventário atualizado de ativos, incluindo equipamentos de TI (notebooks, desktops, monitores, impressoras etc.), com detalhamento de características, localização, detentor, valor de aquisição e depreciação. Isso comprova a execução de um processo de gestão de configuração e ativos de TI.</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…
+://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…
+://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:33:08.485922+00:00</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:35:07.153576+00:00</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>96a850cf85ec953fe1948efc89d29f5d6039068d584194a642a6bfcc33d6ce84</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>q2203ext[A]</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>A evidência demonstra que a organização mantém uma base de dados consolidada e atualizada com as configurações dos serviços e ativos de TI e o relacionamento entre eles. O sistema ASI permite a consulta detalhada de características dos bens (marca, modelo, série, capacidade de HD, processador, memória etc.), localização atual, detentor, histórico de movimentações e inventários. Os relatórios extraídos (Extração Geral - ASI.xlsx, Relatório de Detentores.xlsx, Relatório de Status.xlsx) confirmam a existência de um inventário atualizado e detalhado dos ativos de TI, com informações sobre configurações e localização.</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…
+://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…
+://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:33:08.485922+00:00</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:35:07.153576+00:00</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>96a850cf85ec953fe1948efc89d29f5d6039068d584194a642a6bfcc33d6ce84</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>nao_conforme</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>q2203ext[B]</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>A evidência fornecida não demonstra que a base de dados de configurações é utilizada como insumo para o planejamento e o acompanhamento das mudanças. Embora o sistema ASI possua funcionalidades de gestão de patrimônio e ativos, não há evidência de que essas informações sejam integradas a um processo formal de gestão de mudanças de TI. Os relatórios e funcionalidades apresentados focam na gestão patrimonial e financeira dos bens, mas não mostram seu uso no planejamento ou acompanhamento de mudanças em serviços de TI.</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…
+://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…
+://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…
+://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…
+://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:33:08.485922+00:00</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:35:07.153576+00:00</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>96a850cf85ec953fe1948efc89d29f5d6039068d584194a642a6bfcc33d6ce84</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>nao_conforme</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>q2203ext[C]</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>A evidência não demonstra que o processo de gestão de configuração e ativos está formalizado por meio de norma interna, guia ou instrumento similar com orientações quanto à execução do processo e definição de responsabilidades. O manual online do sistema ASI descreve as funcionalidades do sistema, mas não constitui uma norma ou procedimento formal que defina o processo de gestão de configuração e ativos de TI, suas etapas, responsabilidades e governança. A existência de um sistema e de relatórios não equivale à formalização do processo por meio de documento normativo.</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…
+://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…
+://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…
+://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral
+://outlook.office.com/mail/inbox/id/AAQkAGFmZjUyMjY1LWVmODAtNDIzOS1iNzIzLTMwZmRkY2YxMjE2YwAQAI7EizpPlUxMpnQB6pBhAI…
+://sistemas.mprj.mp.br/asi40/asihelper/help_patrimonio/pa_home.html#consulta_geral</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:33:08.485922+00:00</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:35:07.153576+00:00</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>a) a organização gerencia (inventaria e controla) os dispositivos conectados em sua rede</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>As novas evidências apresentadas (print da tela do Microsoft Intune) demonstram o inventário e o controle efetivo dos dispositivos conectados à rede da organização, sanando a lacuna apontada anteriormente.</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Tabela do Microsoft Intune com listagem de dispositivos (Nome, Estado, Modelo)</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Página 1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:18.359712+00:00</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:43.082734+00:00</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>b) a organização gerencia (inventaria e controla) os softwares instalados nos dispositivos conectados em sua rede</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>As novas evidências apresentadas (print de 'Discovered apps' no Microsoft Intune) confirmam o inventário e controle dos softwares instalados nos dispositivos da organização.</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Lista de Discovered apps no Microsoft Intune admin center</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Página 3</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:18.359712+00:00</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:43.082734+00:00</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>c) a organização gerencia vulnerabilidades técnicas em seus ativos de software, de hardware e de rede críticos para o negócio</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>As evidências apresentadas do Microsoft Defender (Inventories e painel de status) demonstram a gestão de vulnerabilidades e o controle de atualizações nos ativos.</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Defender Inventories (Software, Weaknesses, Exposed devices)</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>Página 4</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:18.359712+00:00</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:43.082734+00:00</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>d) a organização implementa configurações seguras em seus ativos de software, de hardware e de rede críticos para o negócio</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>As evidências apresentadas (relatório Defender365_Security) demonstram a existência e a implementação de políticas de configuração segura em âmbito organizacional.</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Listagem de políticas Defender365 (Adobe, Antivirus, Chrome, etc.)</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>Página 5</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:18.359712+00:00</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:43.082734+00:00</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>e) a organização mantém, monitora e analisa logs de auditoria dos ativos de software, de hardware e de rede críticos para o negócio</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>As evidências apresentadas (Microsoft Purview) demonstram o monitoramento e a análise de logs de auditoria organizacionais.</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Purview eDiscovery/Audit logs (Cases)</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Página 6</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:18.359712+00:00</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:43.082734+00:00</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>g) a organização implementa defesas contra malware (ex: vírus) e outras ameaças cibernéticas (ex: phishing)</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>As evidências apresentadas (relatórios do Microsoft Defender sobre antivírus e bloqueio de ameaças) demonstram a implementação efetiva de defesas contra malware e phishing.</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Relatórios de Antivirus blocks, Phishing e Ransomware</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>Páginas 6 e 7</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:18.359712+00:00</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:43.082734+00:00</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>h) a organização limita e controla o uso de portas, protocolos e serviços de rede nas conexões de sua rede interna com a internet e outras redes externas</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>As evidências apresentadas (tabelas de regras de firewall) demonstram a existência de controle sobre portas, protocolos e serviços nas conexões de rede.</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Tabela de regras de firewall (ID, Name, Service, Action)</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>Página 8</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:18.359712+00:00</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:43.082734+00:00</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>i) a organização implementa defesa de perímetro das conexões de sua rede interna com a internet e outras redes externas</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>As evidências apresentadas (tabelas de regras de bloqueio geográfico) demonstram a implementação de defesas de perímetro na borda da rede.</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Regras de bloqueio de geolocalização e país</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>Página 9</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:18.359712+00:00</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T12:31:43.082734+00:00</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[A]</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>A organização apresentou evidências de que gerencia e inventaria os dispositivos conectados em sua rede corporativa utilizando a ferramenta Microsoft Intune. O painel apresentado exibe uma listagem de ativos (como computadores Dell OptiPlex) com status de conformidade ativo, superando a lacuna de escopo apontada anteriormente (que se limitava aos serviços em nuvem).</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Lista de dispositivos gerenciados pelo Intune (ex: MPRJ-125097, MPRJ-125158) com status 'Em conformidade'</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Página 1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:09:55.871536+00:00</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:10:45.299372+00:00</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[B]</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>A organização apresentou telas de gerenciamento do Microsoft Intune que demonstram o controle dos softwares instalados nos dispositivos da rede corporativa (no painel 'Discovered apps' de dispositivos como MPRJ-149587), listando aplicativos específicos (7-Zip, Adobe Acrobat, Google Chrome, etc.), o que supre a falta de comprovação de inventário de softwares da infraestrutura local.</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Painel 'Discovered apps' do dispositivo MPRJ-149587, contendo a lista de aplicações instaladas</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Página 3</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:09:55.871536+00:00</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:10:45.299372+00:00</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[C]</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Foi comprovada a gestão de vulnerabilidades técnicas em ativos de software por meio do painel do Microsoft Defender ('Inventories' detalhando vulnerabilidades e fraquezas de softwares instalados) e controle de patches no ambiente local por meio do WSUS ('P-WSUS01'), controlando atualizações para diversos grupos de computadores da instituição, sanando a restrição de escopo anterior.</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Painel 'Inventories' do Microsoft Defender contendo status de vulnerabilidade de softwares e painel de controle do WSUS 'P-WSUS01'</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Página 4</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:09:55.871536+00:00</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:10:45.299372+00:00</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[D]</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>A organização apresentou evidências de aplicação de configurações seguras em seus ativos no domínio corporativo ('pgj.rj.gov.br') por meio de GPOs (Group Policy Objects) específicas de segurança para sistema operacional, navegadores (Chrome), antivírus e aplicações (Adobe), garantindo uma padronização segura no parque de TI.</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Políticas de segurança do Active Directory: 'Defender365_Security-Adobe', 'Defender365_Security-Antivirus', 'Defender365_Security-Chrome', 'Defender365_Security-SistemaOperacional'</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Página 5</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:09:55.871536+00:00</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:10:45.299372+00:00</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[E]</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>A organização apresentou evidência de que mantém e analisa logs de auditoria de segurança por meio do console Microsoft Purview ('Audit' e ferramenta 'Data Security Investigations'), demonstrando a centralização e monitoramento de eventos de auditoria aplicados ao ambiente institucional.</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Console Microsoft Purview demonstrando a seção 'Audit' e histórico de investigações de segurança ('Cases')</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>Página 6</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:09:55.871536+00:00</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:10:45.299372+00:00</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[G]</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Foi demonstrada a implementação robusta de defesas contra malware e ameaças cibernéticas (phishing e ransomware) com o Microsoft Defender for Endpoint ativo em 93% dos 10.326 dispositivos da organização. Também foram fornecidos logs de bloqueio de 473 atividades maliciosas por antivírus e de 2.957 e-mails com ameaças (malware/phishing) na borda de e-mail.</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Painéis de 'Phishing and ransomware protection', estatísticas de 'Onboarded devices' indicando 93% de 10.326 ativos protegidos, logs de antivírus e de bloqueios de e-mails</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>Páginas 6 e 7</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:09:55.871536+00:00</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:10:45.299372+00:00</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[H]</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>A organização demonstrou que limita e controla portas, protocolos e serviços de rede em suas conexões corporativas com a internet por meio de regras de firewall ativas contendo perfis de controle de aplicação (App Control), filtro web (Web Filter) e inspeção de tráfego SSL direcionados à sua rede interna, assegurando o controle sobre conexões externas.</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Regras de firewall de saída com filtros de segurança ativos (ex: 'WEBFILTER_NORMAL_SEM_DOWNLOAD', 'WEBFILTER_RESTRITO_GMI')</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>Página 8</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:09:55.871536+00:00</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:10:45.299372+00:00</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[I]</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>A organização apresentou evidências de defesa de perímetro para as conexões de sua rede com a internet por meio de políticas de firewall de borda, incluindo bloqueio de tráfego geográfico ('BLOCK GEO LOCATION' e 'BLOCK PAISES POR ORIGEM') direcionados a países considerados fontes de risco, fornecendo controle efetivo das conexões corporativas externas.</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>Políticas de bloqueio geográfico ('BLOCK GEOLOCATION', 'BLOCK PAISES POR ORIGEM' para China, Coreia do Norte, Rússia, etc.)</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>Página 9</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:09:55.871536+00:00</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T13:10:45.299372+00:00</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[A]</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>A nova evidência (Microsoft Intune admin center) demonstra diretamente o inventário e o controle de dispositivos conectados à rede da organização, com listagem de dispositivos, modelos, fabricantes, sistema operacional, status de conformidade e detalhes de hardware. A lacuna anterior foi integralmente corrigida.</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Imagem: Microsoft Intune admin center - Devices | Windows - listagem de dispositivos MPRJ com modelo, fabricante, sistema operacional e status
+Imagem: MPRJ-149587 | Hardware - detalhes de hardware, sistema operacional, rede e último contato</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>img/00083_10_questão2504.pdf-0001-05.png
+img/00083_10_questão2504.pdf-0002-00.png</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:35:07.154700+00:00</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:36:58.613482+00:00</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[B]</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>A nova evidência (Microsoft Intune - Discovered apps) demonstra diretamente o inventário e controle de softwares instalados nos dispositivos da organização, com listagem de aplicações e versões. A lacuna anterior foi integralmente corrigida.</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Imagem: MPRJ-149587 | Discovered apps - listagem de aplicações instaladas (WhatsApp, 7-Zip, Adobe Acrobat, Google Chrome, MSTeams, etc.) com versões</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>img/00083_10_questão2504.pdf-0003-00.png</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:35:07.154700+00:00</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:36:58.613482+00:00</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[C]</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>A nova evidência (Microsoft Defender - Inventories) demonstra a gestão de vulnerabilidades técnicas em ativos de software, com identificação de fraquezas, ameaças e dispositivos expostos. A imagem do Update Services (WSUS) complementa com o controle de atualizações por grupo de computadores. A lacuna anterior foi integralmente corrigida.</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Imagem: Microsoft Defender Inventories - Software com colunas Weaknesses, Threats, Exposed devices e Impact
+Imagem: Update Services - Computers com resumo de status de atualizações por grupo (DCs, HOMOLOG-WSUS, etc.)</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>img/00083_10_questão2504.pdf-0004-00.png
+img/00083_10_questão2504.pdf-0004-04.png</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:35:07.154700+00:00</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:36:58.613482+00:00</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[D]</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>A nova evidência (Microsoft Intune - Hardware) demonstra configurações seguras do dispositivo, incluindo TPM versão 2.0, BIOS de gerenciamento e conformidade corporativa. A imagem das políticas Defender365_Security complementa com políticas de configuração segura. A lacuna anterior foi integralmente corrigida.</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>Imagem: MPRJ-149587 | Hardware - Versão do TPM 2.0, BIOS de gerenciamento, conformidade corporativa
+Imagem: pgi.rj.gov.br - políticas Defender365_Security (Adobe, Antivirus, Chrome, LoginAccount, Network, SistemaOperacional)</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>img/00083_10_questão2504.pdf-0002-00.png
+img/00083_10_questão2504.pdf-0005-03.png</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:35:07.154700+00:00</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:36:58.613482+00:00</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[E]</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>A nova evidência (Microsoft Purview - eDiscovery Cases) demonstra a existência de casos de investigação de segurança e auditoria, com registro de casos ativos, datas de criação e modificação, evidenciando manutenção, monitoramento e análise de logs/auditoria. A lacuna anterior foi integralmente corrigida.</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Imagem: Microsoft Purview - eDiscovery Cases com 330 itens, casos ativos como 'Requerimento_2904', 'PST-aarino.verga', 'Protocolo-MSG-28set2023'</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>img/00083_10_questão2504.pdf-0006-00.png</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:35:07.154700+00:00</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:36:58.613482+00:00</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[G]</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>A nova evidência (Microsoft Defender) demonstra diretamente a implementação de defesas contra malware e phishing: 473 atividades maliciosas bloqueadas pelo antivírus, 2.957 e-mails maliciosos bloqueados (2.854 phishing, 103 malware), e 93% dos 10.326 dispositivos protegidos. A lacuna anterior foi integralmente corrigida.</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>Imagem: Antivirus blocks - Microsoft Defender Antivirus blocked 473 malicious activities
+Imagem: Blocked emails - 2.957 malicious emails blocked (Phishing 2.854, Malware 103)
+Imagem: Phishing and ransomware protection - 93% of 10.326 devices protected</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>img/00083_10_questão2504.pdf-0006-04.png
+img/00083_10_questão2504.pdf-0007-00.png
+img/00083_10_questão2504.pdf-0007-01.png</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:35:07.154700+00:00</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:36:58.613482+00:00</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[H]</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>A nova evidência (regras de firewall) demonstra diretamente o controle de portas, protocolos e serviços de rede nas conexões da rede interna com a internet, com regras específicas para HTTP/HTTPS, serviços como HTTP, HTTPS, FTP, ALL, e perfis de segurança com deep-inspection. A lacuna anterior foi integralmente corrigida.</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Imagem: Regras de firewall com colunas Service (HTTP, HTTPS, ALL), Action (ACCEPT, DENY), Security Profiles (custom-deep-inspection, FILTER_FULL_SEM_DOWNLOAD, etc.)
+Imagem: Regras BLOCK GEO LOCATION e BLOCK PAISES POR ORIGEM/DESTINO com DENY para países específicos</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>img/00083_10_questão2504.pdf-0008-03.png
+img/00083_10_questão2504.pdf-0009-00.png</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:35:07.154700+00:00</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:36:58.613482+00:00</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>3bf4e2f51c631d1dd8135ad86ceaf7b95dab73f407fff5ee3bb073bc4f2fd457</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>reavaliacao</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>opencodego</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>conforme</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[I]</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>A nova evidência (regras de firewall) demonstra diretamente a defesa de perímetro das conexões da rede interna com a internet, com regras de bloqueio por geolocalização (CHINA, KOREA DO NORTE, RUSSIA, UKRAINE, etc.), bloqueio de países por origem/destino, e perfis de segurança com deep-inspection aplicados às regras de acesso à internet. A lacuna anterior foi integralmente corrigida.</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>00083_10_questão2504.pdf</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Imagem: Regras BLOCK GEO LOCATION e BLOCK PAISES POR ORIGEM/DESTINO com DENY para múltiplos países
+Imagem: Regras de acesso à internet com Security Profiles (custom-deep-inspection, FILTER_FULL_SEM_DOWNLOAD, etc.) aplicados na borda</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>img/00083_10_questão2504.pdf-0008-03.png
+img/00083_10_questão2504.pdf-0009-00.png</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:35:07.154700+00:00</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18T02:36:58.613482+00:00</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X1"/>
+  <autoFilter ref="A1:X43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -640,7 +4716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,8 +4761,42 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>abf0c14116149ec884c3deb7e339f617e594bca8f72469070d714ae8628bd056</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>MPERJ</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>q2201</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-plus</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ausente</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Sem avaliação válida no checkpoint vigente.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -697,7 +4807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,12 +4885,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>A2G4</t>
+          <t>A2G5</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Comitê de TIC ou instância equivalente não instituído formalmente.</t>
+          <t>Comitê de TIC ou instância equivalente sem evidências suficientes de atuação efetiva.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -795,12 +4905,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>6e5206c553b3ec92fe1e1cb2cfe5dfde47b7a705efe034729a3aaa49d502eea5</t>
+          <t>655fee7806a2d0cbabbff5ff4714f8a48e3c2ef55da290f6857342bacb4e99ed</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>b9faa6ae5d9aea2dfd3378936dfcf5dd150f2b6a72f608071680e9ce43bc4c35</t>
+          <t>b1af42185e0ea679053d6a278e6026807c7da6a69ba6bae7424af04cd035fbb4</t>
         </is>
       </c>
     </row>
@@ -812,7 +4922,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>q1001ext[H]</t>
+          <t>q1001ext[F]</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -827,12 +4937,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>A2G6</t>
+          <t>A2G5</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Modelo básico de governança e gestão de TIC inexistente ou insuficiente quanto a papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+          <t>Comitê de TIC ou instância equivalente sem evidências suficientes de atuação efetiva.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -847,12 +4957,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>b4544a5bb5d051c0c6d3e7d7a6c9bf2053ebfd4d0050cb9509bf336615eaf649</t>
+          <t>655fee7806a2d0cbabbff5ff4714f8a48e3c2ef55da290f6857342bacb4e99ed</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>886a9ffb9f95b876463f32392305f749a59147de1d8d617c07d04c17c85e2a32</t>
+          <t>b1af42185e0ea679053d6a278e6026807c7da6a69ba6bae7424af04cd035fbb4</t>
         </is>
       </c>
     </row>
@@ -904,24 +5014,24 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>f82b7224b977cf69bd62e7a465c4e34e0332a8fbbc9e10d2b02cd0f0003e00f6</t>
+          <t>85e604e0dc97ff298b591807f736041a57b42663d6ce73759bb83e095e083979</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IPEM</t>
+          <t>ARRAIAL DO CABO</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>q2101ext[B]</t>
+          <t>q1001ext[F]</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>q2101</t>
+          <t>q1001</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -931,12 +5041,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>A3G9</t>
+          <t>A2G5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+          <t>Comitê de TIC ou instância equivalente sem evidências suficientes de atuação efetiva.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -951,29 +5061,29 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43ba2190a1b495b0eafd783655b03e4973b2f44c81c005f37c0db8ad9d68b383</t>
+          <t>da7297c15375ff47716ec28f901297765317f73670350ed94dd313d2ac4b6d56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>d7afcb2dec8067d66a7c3fcf6590b69f7aac608780e673d290d4e895406a14c9</t>
+          <t>a60b0b6ae04fd985e35b9d26e50691c597c24d9ba7b780b1cca89cf5cdec2f89</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IPEM</t>
+          <t>CAMPOS DOS GOYTACAZES</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>q2101ext[C]</t>
+          <t>q2702ext[A]</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>q2101</t>
+          <t>q2702</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -983,12 +5093,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>A3G9</t>
+          <t>A4G17</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
+          <t>Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1003,12 +5113,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43ba2190a1b495b0eafd783655b03e4973b2f44c81c005f37c0db8ad9d68b383</t>
+          <t>bb1aa3f54f34bbf59a11e6f6f34b7a35ba19e3be1162270ffcd687498d7f3221</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>d7afcb2dec8067d66a7c3fcf6590b69f7aac608780e673d290d4e895406a14c9</t>
+          <t>6a22f28033d6603926403b5f728aba0e87545a4479fd6700d43ba3220c770f40</t>
         </is>
       </c>
     </row>
@@ -1020,12 +5130,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>q2102ext[A]</t>
+          <t>q2101ext[B]</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>q2102</t>
+          <t>q2101</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1035,12 +5145,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>A3G8</t>
+          <t>A3G9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Ausência de aprovação formal do plano de TIC.</t>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1055,29 +5165,29 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1ca03b06161ad16e2fbe02e5909136b940244b5dc2201fb5c25b8e82499ebab8</t>
+          <t>43ba2190a1b495b0eafd783655b03e4973b2f44c81c005f37c0db8ad9d68b383</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4d91e9789223c0e650bd7e0a83147d181fc520bc9d00f72c5a638a1feddfd1a1</t>
+          <t>58c7ffb3a2bf2f0c87d438f3c09111a040716dd523859f69ec60e7c1560f8382</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MPERJ</t>
+          <t>IPEM</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>q2102ext[A]</t>
+          <t>q2101ext[C]</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>q2102</t>
+          <t>q2101</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1087,12 +5197,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>A3G8</t>
+          <t>A3G9</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Ausência de aprovação formal do plano de TIC.</t>
+          <t>Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1107,29 +5217,29 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11be4a0823100a5f0a721cbbb153ede75b6531fd3a6cdec779576f6183354c89</t>
+          <t>43ba2190a1b495b0eafd783655b03e4973b2f44c81c005f37c0db8ad9d68b383</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0cd31fcde226194df22a2945ae8ac59af757785d35d6095b938dc5e5bb6a564e</t>
+          <t>58c7ffb3a2bf2f0c87d438f3c09111a040716dd523859f69ec60e7c1560f8382</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>JUCERJA</t>
+          <t>IPEM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>q2802ext[C]</t>
+          <t>q2102ext[A]</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>q2802</t>
+          <t>q2102</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1139,12 +5249,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>A6G23</t>
+          <t>A3G8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Contratações de TIC sem alinhamento demonstrado ao planejamento de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+          <t>Ausência de aprovação formal do plano de TIC.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1159,29 +5269,29 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>a4127c1213e480c6bc9a6a70c5fad239f8ac5e6a81cb9d1c9e103f99a7ca7da7</t>
+          <t>1ca03b06161ad16e2fbe02e5909136b940244b5dc2201fb5c25b8e82499ebab8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>07e0ee68c492b9787e1d856e2637c47c8486223e99b06cdacbf9ed70170a39e3</t>
+          <t>9fe0519e00a2b6a6be6e3e9a366bb939c4897cb97a96dd4e99dce31bf2c1f2dd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RIO DAS OSTRAS</t>
+          <t>ISP</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>q2802ext[C]</t>
+          <t>q2102ext[C]</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>q2802</t>
+          <t>q2102</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1191,12 +5301,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>A3G11</t>
+          <t>A6G23</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Plano de TIC sem vínculo demonstrado com orçamento e contratações de TIC</t>
+          <t>Contratações de TIC sem alinhamento demonstrado ao planejamento de TIC, ao plano de contratações ou à proposta orçamentária.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1211,24 +5321,24 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5a287ebd339e6d1ed67e0c28f7df23667eaa6fd387aa4e75db2cc6e546cfc55b</t>
+          <t>1e242c11aef36be7093cf59e54ceec1788be60a54ff480afe76889674d39197a</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>a996db0f6632002fda807816e285986f57feda023d7ac3e01711254a441daade</t>
+          <t>a2f3c163758bb705b0f806b527879e979390755cb3f310ca35b88a516bccfbe1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RIO DAS OSTRAS</t>
+          <t>ISP</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>q2802ext[D]</t>
+          <t>q2802ext[C]</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1243,12 +5353,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>A3G11</t>
+          <t>A6G23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Plano de TIC sem vínculo demonstrado com orçamento e contratações de TIC</t>
+          <t>Contratações de TIC sem alinhamento demonstrado ao planejamento de TIC, ao plano de contratações ou à proposta orçamentária.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1263,29 +5373,29 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5a287ebd339e6d1ed67e0c28f7df23667eaa6fd387aa4e75db2cc6e546cfc55b</t>
+          <t>1e242c11aef36be7093cf59e54ceec1788be60a54ff480afe76889674d39197a</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>a996db0f6632002fda807816e285986f57feda023d7ac3e01711254a441daade</t>
+          <t>a2f3c163758bb705b0f806b527879e979390755cb3f310ca35b88a516bccfbe1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RIOPREVIDENCIA</t>
+          <t>MPERJ</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>q2802ext[C]</t>
+          <t>q2102ext[A]</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>q2802</t>
+          <t>q2102</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1295,12 +5405,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>A6G23</t>
+          <t>A3G8</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Contratações de TIC sem alinhamento demonstrado ao planejamento de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+          <t>Ausência de aprovação formal do plano de TIC.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1315,29 +5425,29 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5379c6e851d48be36247159edb6e1065a95ca836f101794bda5770ea9ee7414d</t>
+          <t>11be4a0823100a5f0a721cbbb153ede75b6531fd3a6cdec779576f6183354c89</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8f93a6d0f75241947bf13c97e2954ceb362a048497ed3b9421dc569188a3c113</t>
+          <t>675f6d8acfe60fc4019d10881a76c0991fdfa89093843772d9c9710fdc81b013</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RIOPREVIDENCIA</t>
+          <t>MPERJ</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>q2802ext[D]</t>
+          <t>q2201ext[A]</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>q2802</t>
+          <t>q2201</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1347,12 +5457,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>A6G23</t>
+          <t>A5G22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Contratações de TIC sem alinhamento demonstrado ao planejamento de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+          <t>Inexistência ou insuficiência do catálogo de serviços de TIC.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1367,29 +5477,29 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5379c6e851d48be36247159edb6e1065a95ca836f101794bda5770ea9ee7414d</t>
+          <t>8d925d5237887e57e31b795b34166bd32fff1d92f79425454d08b58b030eb0e2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8f93a6d0f75241947bf13c97e2954ceb362a048497ed3b9421dc569188a3c113</t>
+          <t>2399c131d8c409c9f8d661b7160e2f3f9a1b0abbbfa715a907d055075d422c81</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RIO DAS OSTRAS</t>
+          <t>MPERJ</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>q1001ext[F]</t>
+          <t>q2201ext[B]</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>q1001</t>
+          <t>q2201</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1399,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>A2G5</t>
+          <t>A5G22</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Comitê de TIC ou instância equivalente sem evidências suficientes de atuação efetiva.</t>
+          <t>Inexistência ou insuficiência do catálogo de serviços de TIC.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1419,29 +5529,29 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48abd0aac78955d87a7012b357b9d111ce170fa41b3abd11daa342b0c5b71eca</t>
+          <t>8d925d5237887e57e31b795b34166bd32fff1d92f79425454d08b58b030eb0e2</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>66ad62406f0387077c3a475bded389c31cdf2d2ffb7a8bc6377b69a8c559f463</t>
+          <t>2399c131d8c409c9f8d661b7160e2f3f9a1b0abbbfa715a907d055075d422c81</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RIO DAS OSTRAS</t>
+          <t>MPERJ</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>q1001ext[H]</t>
+          <t>q2201ext[C]</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>q1001</t>
+          <t>q2201</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1451,12 +5561,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>A2G6</t>
+          <t>A5G22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Modelo básico de governança e gestão de TIC inexistente ou insuficiente quanto a papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.</t>
+          <t>Inexistência ou insuficiência do catálogo de serviços de TIC.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1471,29 +5581,29 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4947339001c7c65c38dbf81493f67bc4d5bce1823feda0a427bd888240dbb1eb</t>
+          <t>8d925d5237887e57e31b795b34166bd32fff1d92f79425454d08b58b030eb0e2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>ea2bb031a2cc311aec4a489f9aefc33f9917f2d18104c87eea7d5ddd4280dc83</t>
+          <t>2399c131d8c409c9f8d661b7160e2f3f9a1b0abbbfa715a907d055075d422c81</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SÃO PEDRO DA ALDEIA</t>
+          <t>MPERJ</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>q1001ext[E]</t>
+          <t>q2201ext[D]</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>q1001</t>
+          <t>q2201</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1503,12 +5613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>A2G4</t>
+          <t>A5G19</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Comitê de TIC ou instância equivalente não instituído formalmente.</t>
+          <t>Ausência ou fragilidade na definição e no monitoramento de níveis mínimos de serviço de TIC.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,29 +5633,29 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6bcd318d42529bb6f7e25de38a682cbb68bd10b2f88b7e7676c59a4037f50d0d</t>
+          <t>d20605948e3bfe41c1505cd2f9629aee86295dab1f8e63dfd7b8f487bd036238</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>763777a9b432090ec08d104c2a4ad0cd85250ae7a2820778e5fc5ff3e466a4a7</t>
+          <t>99ea821e543f740b58cfc905629ade5cf60ec94e40ea9798bde7b4ce69de75ee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TJRJ</t>
+          <t>MPERJ</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>q2708[B]</t>
+          <t>q2201ext[E]</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>q2708</t>
+          <t>q2201</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1555,17 +5665,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>A4G13</t>
+          <t>A5G19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
+          <t>Ausência ou fragilidade na definição e no monitoramento de níveis mínimos de serviço de TIC.</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>afastada_na_data_base</t>
+          <t>corrigida_posteriormente</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1575,69 +5685,745 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>662910b48bdb1da9dbb48e16c2d0675ba412b29a0d31945a320da9dc32a0a42e</t>
+          <t>d20605948e3bfe41c1505cd2f9629aee86295dab1f8e63dfd7b8f487bd036238</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5947c0e71af901c2d3296bd48e6be42702c1c7faf261df1722bae0c7e30b4f19</t>
+          <t>99ea821e543f740b58cfc905629ade5cf60ec94e40ea9798bde7b4ce69de75ee</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>NOVA IGUAÇU</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>q1001ext[F]</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>q1001</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>A2G5</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Comitê de TIC ou instância equivalente sem evidências suficientes de atuação efetiva.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>corrigida_posteriormente</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>b03dff3874bef58f03f7c04245af229af66f922591a3dfdb66006c568d3453ac</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>51ec3f92683dd454fc718981b604591694fc3fd836a7a8ea1d713a8b8f3ffb01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>RIOPREVIDENCIA</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>q2203ext[A]</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>A5G20</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>afastada_na_data_base</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>cfa859c86c90ed1cd3e9f928507d677832e047a298b0b9c180c4118f90cd03ee</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>d1e603b7da9ed582b6ea5d86277fe491d07c43de243f1fb7a2dd8c372412a4ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SEDEC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[A]</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>A5G20</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>corrigida_posteriormente</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0d6767c8b7e4d020c44d79e7ae122d84dd84737f8897c75bddbbe47a8258e4bf</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>733b1db5cc8cc0e839c3224f05a379c3a768496d0eeec3d3e44a505a26e5195e</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SEDEC</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>q2504ext[B]</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>q2504</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>A5G20</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>corrigida_posteriormente</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0d6767c8b7e4d020c44d79e7ae122d84dd84737f8897c75bddbbe47a8258e4bf</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>733b1db5cc8cc0e839c3224f05a379c3a768496d0eeec3d3e44a505a26e5195e</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>RIO DAS OSTRAS</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>q1001ext[F]</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>q1001</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>A2G5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Comitê de TIC ou instância equivalente sem evidências suficientes de atuação efetiva.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>corrigida_posteriormente</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>48abd0aac78955d87a7012b357b9d111ce170fa41b3abd11daa342b0c5b71eca</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>6af1da472f4afd0c58c2c6b97cfb20dcf15a06e62240d6983c5b013248d786d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>q2204ext[A]</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>q2204</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>A5G21</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>corrigida_posteriormente</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>d76bfac5e35903c86f4bd5ac1592c828d4f01c8a83309674f46394c2db40a285</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>efbee928334aa270809380de184db4b032a9e5f7fc8fe0a21f4144bd1cba7722</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>q2204ext[E]</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>q2204</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>A5G21</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>corrigida_posteriormente</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>d76bfac5e35903c86f4bd5ac1592c828d4f01c8a83309674f46394c2db40a285</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>efbee928334aa270809380de184db4b032a9e5f7fc8fe0a21f4144bd1cba7722</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SETD</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>q2204ext[A]</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>q2204</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>A5G21</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>corrigida_posteriormente</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>99955ad1d1bdcd553f220d26d454f2b029a610fe56c7f18eecfefcba2a276fb9</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>bc108e0c2715ae6be315da7ac29a42711f2305677fff57db8c22e1451757bd73</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SETD</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>q2204ext[D]</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>q2204</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>A5G21</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>corrigida_posteriormente</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99955ad1d1bdcd553f220d26d454f2b029a610fe56c7f18eecfefcba2a276fb9</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>bc108e0c2715ae6be315da7ac29a42711f2305677fff57db8c22e1451757bd73</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SETD</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>q2204ext[E]</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>q2204</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>A5G21</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do processo de gestão de incidentes de TIC.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>corrigida_posteriormente</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>99955ad1d1bdcd553f220d26d454f2b029a610fe56c7f18eecfefcba2a276fb9</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>bc108e0c2715ae6be315da7ac29a42711f2305677fff57db8c22e1451757bd73</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>TJRJ</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>q2708[B]</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>q2708</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>A4G13</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>afastada_na_data_base</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>662910b48bdb1da9dbb48e16c2d0675ba412b29a0d31945a320da9dc32a0a42e</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>6fe9bf99ab1c2bb2929b4c99ce23556623e259e7261ecc51fd8fe56a4884c82f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TJRJ</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>q2708[D]</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>q2708</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Item saneado por parecer consolidado da seção 1.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>A4G13</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Ausência de cargos, funções, perfis ou ocupações específicas de TIC e segurança da informação.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>afastada_na_data_base</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>662910b48bdb1da9dbb48e16c2d0675ba412b29a0d31945a320da9dc32a0a42e</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5947c0e71af901c2d3296bd48e6be42702c1c7faf261df1722bae0c7e30b4f19</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>6fe9bf99ab1c2bb2929b4c99ce23556623e259e7261ecc51fd8fe56a4884c82f</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TJRJ</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>q2804[A]</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>q2804</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>A6G24</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Contratações de TIC sem análise prévia e aprovação técnica obrigatória da área de TIC.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>afastada_na_data_base</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>d2d32d7833d8ac1c861def6334af160790f6cd51c078d34a91ac045ce55704e3</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1bce1ec9d9a7225e4c2c55ca67a88be59942f786879f5c71b08b2225843b7b69</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>UERJ</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>q2203ext[A]</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>q2203</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Item saneado por parecer consolidado da seção 1.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>A5G20</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Inexistência ou fragilidade do inventário de ativos de TIC.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>afastada_na_data_base</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>5e5d2b29b820db96a49c59122ed15b34d76bd11aa4adbed3f146ed1bef9a4b88</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>0d68e14390562b8c0f43293f205e677ca041e64d580adf3c299db1e4c2bac013</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J18"/>
+  <autoFilter ref="A1:J31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>